--- a/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-observation-sur-echelle-douleur.xlsx
+++ b/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-observation-sur-echelle-douleur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-01T13:19:09+00:00</t>
+    <t>2025-09-02T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -478,7 +478,7 @@
 </t>
   </si>
   <si>
-    <t>FR Repeat Number</t>
+    <t>Fr Repeat Number</t>
   </si>
   <si>
     <t>Numéro d'occurrence de l'acte ou de l'observation (équivalent CDA repeatNumber)</t>
